--- a/diseases/d240/2010-2014.xlsx
+++ b/diseases/d240/2010-2014.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -18555,7 +18555,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -23322,7 +23322,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -24684,7 +24684,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -25819,7 +25819,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -28316,7 +28316,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -29451,7 +29451,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -30586,7 +30586,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -31948,7 +31948,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -33083,7 +33083,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -34218,7 +34218,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -35580,7 +35580,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -36715,7 +36715,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -37850,7 +37850,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -39212,7 +39212,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -40347,7 +40347,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -41482,7 +41482,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -42844,7 +42844,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -43979,7 +43979,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -45341,7 +45341,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -46476,7 +46476,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -47611,7 +47611,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -48973,7 +48973,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">

--- a/diseases/d240/2010-2014.xlsx
+++ b/diseases/d240/2010-2014.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -18555,7 +18555,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -23322,7 +23322,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -24684,7 +24684,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -25819,7 +25819,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -28316,7 +28316,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -29451,7 +29451,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -30586,7 +30586,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -31948,7 +31948,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -33083,7 +33083,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -34218,7 +34218,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -35580,7 +35580,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -36715,7 +36715,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -37850,7 +37850,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -39212,7 +39212,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -40347,7 +40347,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -41482,7 +41482,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -42844,7 +42844,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -43979,7 +43979,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -45341,7 +45341,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -46476,7 +46476,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -47611,7 +47611,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -48973,7 +48973,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
